--- a/tech_ARC_simple_v2.xlsx
+++ b/tech_ARC_simple_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54AD6E2-225E-46EE-A792-ABD605C3E19A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680195D5-C563-4DF0-A964-5E90D92CEED5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
@@ -224,7 +224,7 @@
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7" refreshError="1"/>
@@ -232,20 +232,8 @@
       <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10" refreshError="1"/>
       <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12">
-        <row r="21">
-          <cell r="C21">
-            <v>2.0114159106083146E-8</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13">
-        <row r="21">
-          <cell r="C21">
-            <v>9.4856034682359522E-2</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -261,6 +249,11 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
+        <row r="4">
+          <cell r="B4">
+            <v>3.4804999999999998E-4</v>
+          </cell>
+        </row>
         <row r="9">
           <cell r="B9">
             <v>1.1204000000000001</v>
